--- a/public/assets/template_import_jadwal.xlsx
+++ b/public/assets/template_import_jadwal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjekBaru\kp_dela_hanggar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFDB5A56-3C43-42F2-86B9-0AA002CA0419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E357066E-ED2F-4617-85B3-95E6561099AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{80F04221-D13C-488C-A413-CCAA021ABC8A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Nama Karyawan</t>
   </si>
@@ -51,17 +51,26 @@
     <t>Memberikan Makan Sapi</t>
   </si>
   <si>
-    <t>Mahardi Agus</t>
+    <t>Jaya</t>
+  </si>
+  <si>
+    <t>Memberikan Makan Ayam</t>
+  </si>
+  <si>
+    <t>Muji</t>
+  </si>
+  <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>10:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +83,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,11 +111,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,11 +429,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C3ACF01-8A0C-4D08-9CFC-79A7CC4B6BD7}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="17.109375" customWidth="1"/>
@@ -427,10 +441,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
@@ -447,11 +461,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>45940</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.41666666666666669</v>
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -459,14 +473,35 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1823798</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3">
-        <v>17826387</v>
+      <c r="F3" s="1">
+        <v>2173127</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>